--- a/static/data/exports/Retro_BR_GE-BP_2020.xlsx
+++ b/static/data/exports/Retro_BR_GE-BP_2020.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,6 +576,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
       <c r="R2" t="n">
         <v>41</v>
       </c>
@@ -635,6 +638,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
       <c r="R3" t="n">
         <v>41</v>
       </c>
@@ -694,6 +700,9 @@
           <t>BYPP</t>
         </is>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
       <c r="R4" t="n">
         <v>41</v>
       </c>
@@ -753,6 +762,9 @@
           <t>RLSP</t>
         </is>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
         <v>41</v>
       </c>
@@ -812,6 +824,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
       <c r="R6" t="n">
         <v>41</v>
       </c>
@@ -871,6 +886,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
       <c r="R7" t="n">
         <v>41</v>
       </c>
@@ -930,6 +948,9 @@
           <t>JAC</t>
         </is>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
       <c r="R8" t="n">
         <v>41</v>
       </c>
@@ -989,6 +1010,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
       <c r="R9" t="n">
         <v>41</v>
       </c>
@@ -1048,6 +1072,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
       <c r="R10" t="n">
         <v>41</v>
       </c>
@@ -1107,6 +1134,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
       <c r="R11" t="n">
         <v>41</v>
       </c>
@@ -1166,6 +1196,9 @@
           <t>BYPP</t>
         </is>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
       <c r="R12" t="n">
         <v>41</v>
       </c>
@@ -1225,6 +1258,9 @@
           <t>RLSP</t>
         </is>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
       <c r="R13" t="n">
         <v>41</v>
       </c>
@@ -1284,6 +1320,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
       <c r="R14" t="n">
         <v>41</v>
       </c>
@@ -1343,6 +1382,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
       <c r="R15" t="n">
         <v>41</v>
       </c>
@@ -1402,6 +1444,9 @@
           <t>JAC</t>
         </is>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
         <v>41</v>
       </c>
@@ -1461,6 +1506,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
       <c r="R17" t="n">
         <v>41</v>
       </c>
@@ -1520,6 +1568,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
       <c r="R18" t="n">
         <v>41</v>
       </c>
@@ -1579,6 +1630,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
       <c r="R19" t="n">
         <v>41</v>
       </c>
@@ -1638,6 +1692,9 @@
           <t>BYPP</t>
         </is>
       </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
       <c r="R20" t="n">
         <v>41</v>
       </c>
@@ -1697,6 +1754,9 @@
           <t>RLSP</t>
         </is>
       </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
       <c r="R21" t="n">
         <v>41</v>
       </c>
@@ -1756,6 +1816,9 @@
           <t>JAC</t>
         </is>
       </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
       <c r="R22" t="n">
         <v>41</v>
       </c>
@@ -1815,6 +1878,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
       <c r="R23" t="n">
         <v>41</v>
       </c>
@@ -1874,6 +1940,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
       <c r="R24" t="n">
         <v>41</v>
       </c>
@@ -1933,6 +2002,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
       <c r="R25" t="n">
         <v>41</v>
       </c>
@@ -1992,6 +2064,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
       <c r="R26" t="n">
         <v>41</v>
       </c>
@@ -2051,6 +2126,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
       <c r="R27" t="n">
         <v>41</v>
       </c>
@@ -2110,6 +2188,9 @@
           <t>RLSP</t>
         </is>
       </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
       <c r="R28" t="n">
         <v>41</v>
       </c>
@@ -2169,6 +2250,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
       <c r="R29" t="n">
         <v>41</v>
       </c>
@@ -2228,6 +2312,9 @@
           <t>JAC</t>
         </is>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
       <c r="R30" t="n">
         <v>41</v>
       </c>
@@ -2287,6 +2374,9 @@
           <t>BYPP</t>
         </is>
       </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
       <c r="R31" t="n">
         <v>41</v>
       </c>
@@ -2346,6 +2436,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
       <c r="R32" t="n">
         <v>41</v>
       </c>
@@ -2405,6 +2498,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
       <c r="R33" t="n">
         <v>41</v>
       </c>
@@ -2464,6 +2560,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
       <c r="R34" t="n">
         <v>41</v>
       </c>
@@ -2523,6 +2622,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
       <c r="R35" t="n">
         <v>41</v>
       </c>
@@ -2582,6 +2684,9 @@
           <t>RLSP</t>
         </is>
       </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
       <c r="R36" t="n">
         <v>41</v>
       </c>
@@ -2641,6 +2746,9 @@
           <t>BYPP</t>
         </is>
       </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
       <c r="R37" t="n">
         <v>41</v>
       </c>
@@ -2700,6 +2808,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
       <c r="R38" t="n">
         <v>41</v>
       </c>
@@ -2759,6 +2870,9 @@
           <t>JAC</t>
         </is>
       </c>
+      <c r="Q39" t="b">
+        <v>0</v>
+      </c>
       <c r="R39" t="n">
         <v>41</v>
       </c>
@@ -2818,6 +2932,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
       <c r="R40" t="n">
         <v>41</v>
       </c>
@@ -2877,6 +2994,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
       <c r="R41" t="n">
         <v>41</v>
       </c>
@@ -2936,6 +3056,9 @@
           <t>JD(U)</t>
         </is>
       </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
       <c r="R42" t="n">
         <v>41</v>
       </c>
@@ -2995,6 +3118,9 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
       <c r="R43" t="n">
         <v>41</v>
       </c>
@@ -3054,6 +3180,9 @@
           <t>BYPP</t>
         </is>
       </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
       <c r="R44" t="n">
         <v>41</v>
       </c>
@@ -3113,6 +3242,9 @@
           <t>NOTA</t>
         </is>
       </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
       <c r="R45" t="n">
         <v>41</v>
       </c>
@@ -3172,6 +3304,9 @@
           <t>RLSP</t>
         </is>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
       <c r="R46" t="n">
         <v>41</v>
       </c>
@@ -3231,6 +3366,9 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
       <c r="R47" t="n">
         <v>41</v>
       </c>
@@ -3290,6 +3428,9 @@
           <t>JAC</t>
         </is>
       </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
       <c r="R48" t="n">
         <v>41</v>
       </c>
@@ -3348,6 +3489,9 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="Q49" t="b">
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>41</v>
